--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20261016.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20261016.xlsx
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>211,110,000</t>
+          <t>105,970,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>105,970,000</t>
+          <t>211,110,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>新普</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>80,980,000</t>
+          <t>8,564,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>新普</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>8,564,000</t>
+          <t>12,488,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>12,488,000</t>
+          <t>80,980,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>14,390,000</t>
+          <t>28,310,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>28,310,000</t>
+          <t>14,390,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
